--- a/input/scenario_retirementAgeFixed.xlsx
+++ b/input/scenario_retirementAgeFixed.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aburdett/Library/CloudStorage/Box-Box/ESPON - OVERLAP/_countries/PL/additional_required_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E4E6B1-FFFE-974F-868C-7FE688E1DD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F0E12F-D5EF-4ED1-A0AF-013653D04D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35320" yWindow="-100" windowWidth="29000" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="PL" sheetId="13" r:id="rId1"/>
+    <sheet name="IT" sheetId="13" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -366,9 +366,9 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:C52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -379,7 +379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -390,7 +390,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -401,51 +401,51 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>2012</v>
       </c>
       <c r="B4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>2013</v>
       </c>
       <c r="B5">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>2014</v>
       </c>
       <c r="B6">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>2015</v>
       </c>
       <c r="B7">
+        <v>66</v>
+      </c>
+      <c r="C7">
         <v>65</v>
       </c>
-      <c r="C7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -453,10 +453,10 @@
         <v>66</v>
       </c>
       <c r="C8">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -464,480 +464,480 @@
         <v>66</v>
       </c>
       <c r="C9">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>2018</v>
       </c>
       <c r="B10">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>2019</v>
       </c>
       <c r="B11">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>2020</v>
       </c>
       <c r="B12">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C12">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>2021</v>
       </c>
       <c r="B13">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C13">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>2022</v>
       </c>
       <c r="B14">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C14">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>2023</v>
       </c>
       <c r="B15">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C15">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>2024</v>
       </c>
       <c r="B16">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C16">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>2025</v>
       </c>
       <c r="B17">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C17">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>2026</v>
       </c>
       <c r="B18">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C18">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>2027</v>
       </c>
       <c r="B19">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C19">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>2028</v>
       </c>
       <c r="B20">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C20">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>2029</v>
       </c>
       <c r="B21">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C21">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>2030</v>
       </c>
       <c r="B22">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C22">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>2031</v>
       </c>
       <c r="B23">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C23">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>2032</v>
       </c>
       <c r="B24">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C24">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>2033</v>
       </c>
       <c r="B25">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C25">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>2034</v>
       </c>
       <c r="B26">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C26">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>2035</v>
       </c>
       <c r="B27">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C27">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>2036</v>
       </c>
       <c r="B28">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C28">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>2037</v>
       </c>
       <c r="B29">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C29">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>2038</v>
       </c>
       <c r="B30">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C30">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>2039</v>
       </c>
       <c r="B31">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C31">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>2040</v>
       </c>
       <c r="B32">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C32">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>2041</v>
       </c>
       <c r="B33">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C33">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>2042</v>
       </c>
       <c r="B34">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C34">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>2043</v>
       </c>
       <c r="B35">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C35">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>2044</v>
       </c>
       <c r="B36">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C36">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>2045</v>
       </c>
       <c r="B37">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C37">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>2046</v>
       </c>
       <c r="B38">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C38">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>2047</v>
       </c>
       <c r="B39">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C39">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>2048</v>
       </c>
       <c r="B40">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C40">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>2049</v>
       </c>
       <c r="B41">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C41">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>2050</v>
       </c>
       <c r="B42">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C42">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>2051</v>
       </c>
       <c r="B43">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C43">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>2052</v>
       </c>
       <c r="B44">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C44">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>2053</v>
       </c>
       <c r="B45">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C45">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>2054</v>
       </c>
       <c r="B46">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C46">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>2055</v>
       </c>
       <c r="B47">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C47">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>2056</v>
       </c>
       <c r="B48">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C48">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>2057</v>
       </c>
       <c r="B49">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C49">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>2058</v>
       </c>
       <c r="B50">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C50">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>2059</v>
       </c>
       <c r="B51">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C51">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>2060</v>
       </c>
       <c r="B52">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C52">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/input/scenario_retirementAgeFixed.xlsx
+++ b/input/scenario_retirementAgeFixed.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F0E12F-D5EF-4ED1-A0AF-013653D04D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88EB1E74-CF31-4373-B8AD-6C68CD86E9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="IT" sheetId="13" r:id="rId1"/>
+    <sheet name="EL" sheetId="13" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -366,9 +366,9 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:C52"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -379,7 +379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -387,10 +387,10 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -398,109 +398,109 @@
         <v>65</v>
       </c>
       <c r="C3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2012</v>
       </c>
       <c r="B4">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2013</v>
       </c>
       <c r="B5">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2014</v>
       </c>
       <c r="B6">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2015</v>
       </c>
       <c r="B7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2016</v>
       </c>
       <c r="B8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2017</v>
       </c>
       <c r="B9">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2018</v>
       </c>
       <c r="B10">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2019</v>
       </c>
       <c r="B11">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2020</v>
       </c>
       <c r="B12">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -511,7 +511,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -522,7 +522,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -533,7 +533,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -544,7 +544,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -555,7 +555,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -566,7 +566,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2027</v>
       </c>
@@ -577,7 +577,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2028</v>
       </c>
@@ -588,7 +588,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2029</v>
       </c>
@@ -599,7 +599,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -610,7 +610,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2031</v>
       </c>
@@ -621,7 +621,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -632,7 +632,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2033</v>
       </c>
@@ -643,7 +643,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2034</v>
       </c>
@@ -654,7 +654,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -665,7 +665,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2036</v>
       </c>
@@ -676,7 +676,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2037</v>
       </c>
@@ -687,7 +687,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2038</v>
       </c>
@@ -698,7 +698,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2039</v>
       </c>
@@ -709,235 +709,235 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2040</v>
       </c>
       <c r="B32">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C32">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2041</v>
       </c>
       <c r="B33">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C33">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2042</v>
       </c>
       <c r="B34">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C34">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2043</v>
       </c>
       <c r="B35">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C35">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2044</v>
       </c>
       <c r="B36">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C36">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2045</v>
       </c>
       <c r="B37">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C37">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2046</v>
       </c>
       <c r="B38">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C38">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2047</v>
       </c>
       <c r="B39">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C39">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2048</v>
       </c>
       <c r="B40">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C40">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2049</v>
       </c>
       <c r="B41">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C41">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2050</v>
       </c>
       <c r="B42">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C42">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2051</v>
       </c>
       <c r="B43">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C43">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2052</v>
       </c>
       <c r="B44">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C44">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2053</v>
       </c>
       <c r="B45">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C45">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2054</v>
       </c>
       <c r="B46">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C46">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2055</v>
       </c>
       <c r="B47">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C47">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2056</v>
       </c>
       <c r="B48">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C48">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2057</v>
       </c>
       <c r="B49">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C49">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2058</v>
       </c>
       <c r="B50">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C50">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2059</v>
       </c>
       <c r="B51">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C51">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2060</v>
       </c>
       <c r="B52">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C52">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
